--- a/artfynd/A 25541-2023 artfynd.xlsx
+++ b/artfynd/A 25541-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115342701</v>
+        <v>115459888</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>241</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gryten (Västra Degerforsområdet), Vrm</t>
+          <t>Grytens gammelskogar, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464053</v>
+        <v>464123</v>
       </c>
       <c r="R2" t="n">
-        <v>6566550</v>
+        <v>6566478</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,74 +756,69 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115343415</v>
+        <v>115459893</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1179</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gryten (Västra Degerforsområdet), Vrm</t>
+          <t>Grytens gammelskogar, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463953</v>
+        <v>464127</v>
       </c>
       <c r="R3" t="n">
-        <v>6566494</v>
+        <v>6566485</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:37</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:37</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,31 +858,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115340501</v>
+        <v>115459791</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,42 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gryten (Västra Degerforsområdet), Vrm</t>
+          <t>Grytens gammelskogar, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464084</v>
+        <v>464015</v>
       </c>
       <c r="R4" t="n">
-        <v>6566521</v>
+        <v>6566447</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,27 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,31 +960,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115459774</v>
+        <v>115459953</v>
       </c>
       <c r="B5" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463998</v>
+        <v>464017</v>
       </c>
       <c r="R5" t="n">
-        <v>6566463</v>
+        <v>6566430</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1118,11 +1063,6 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1135,6 +1075,551 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>115459784</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97453</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1841</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedflikmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lophozia guttulata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Grytens gammelskogar, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>464132</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6566478</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>115459774</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Grytens gammelskogar, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>463998</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6566463</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>115342701</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gryten, Västra Degerforsområdet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>464053</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6566550</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>115343415</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gryten, Västra Degerforsområdet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>463953</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6566494</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>115340501</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gryten, Västra Degerforsområdet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>464084</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6566521</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25541-2023 artfynd.xlsx
+++ b/artfynd/A 25541-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115459888</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115459893</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115459791</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115459953</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115459784</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115459774</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115342701</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1503,6 +1543,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115343415</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1620,8 +1665,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115340501</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>